--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Septiembre 06-2025</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6562.463</v>
+        <v>6562.019</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.3e-05</v>
+        <v>-0.000121</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.9468</v>
+        <v>-36.2429</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3083</v>
+        <v>0.269</v>
       </c>
       <c r="G14" t="n">
-        <v>1.583</v>
+        <v>1.081</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8633</v>
+        <v>0.4337</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julio 22-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -872,28 +872,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6562.406</v>
+        <v>6561.891</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.2e-05</v>
+        <v>-0.00014</v>
       </c>
       <c r="E15" t="n">
-        <v>-18.5634</v>
+        <v>-42.063</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3182</v>
+        <v>0.2086</v>
       </c>
       <c r="G15" t="n">
-        <v>1.476</v>
+        <v>0.959</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8136</v>
+        <v>0.2413</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -902,28 +902,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6562.019</v>
+        <v>6562.148</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.000121</v>
+        <v>-0.000101</v>
       </c>
       <c r="E16" t="n">
-        <v>-36.2429</v>
+        <v>-30.3483</v>
       </c>
       <c r="F16" t="n">
-        <v>0.269</v>
+        <v>0.3547</v>
       </c>
       <c r="G16" t="n">
-        <v>1.081</v>
+        <v>1.051</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4337</v>
+        <v>0.4543</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -932,28 +932,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6561.891</v>
+        <v>6562.177</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.00014</v>
+        <v>-9.7e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>-42.063</v>
+        <v>-29.0068</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2086</v>
+        <v>0.3875</v>
       </c>
       <c r="G17" t="n">
-        <v>0.959</v>
+        <v>1.134</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2413</v>
+        <v>0.6049</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -962,28 +962,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6562.148</v>
+        <v>6562.166</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.000101</v>
+        <v>-9.8e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>-30.3483</v>
+        <v>-29.5136</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3547</v>
+        <v>0.3471</v>
       </c>
       <c r="G18" t="n">
-        <v>1.051</v>
+        <v>1.111</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4543</v>
+        <v>0.5417</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6562.177</v>
+        <v>6562.141</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.7e-05</v>
+        <v>-0.000102</v>
       </c>
       <c r="E19" t="n">
-        <v>-29.0068</v>
+        <v>-30.6728</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3875</v>
+        <v>0.3028</v>
       </c>
       <c r="G19" t="n">
-        <v>1.134</v>
+        <v>1.096</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6049</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1022,111 +1022,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.166</v>
+        <v>6562.106</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.8e-05</v>
+        <v>-0.000108</v>
       </c>
       <c r="E20" t="n">
-        <v>-29.5136</v>
+        <v>-32.2395</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3471</v>
+        <v>0.2979</v>
       </c>
       <c r="G20" t="n">
-        <v>1.111</v>
+        <v>1.046</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5417</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Agosto 26-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6562.486</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-5e-05</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-14.8782</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.4537</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.9314</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Agosto 28-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>6562.141</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-0.000102</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-30.6728</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.3028</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.469</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Septiembre 07-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>6562.106</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-0.000108</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-32.2395</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.2979</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.046</v>
-      </c>
-      <c r="H23" t="n">
         <v>0.4257</v>
       </c>
     </row>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,20 +451,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Velocidad [km/s]</t>
+          <t>Velocidad obs. [km/s]</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Velocidad heliocéntrica [km/s]</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Profundidad / Altura</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>FWHM [Å]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>EW [Å]</t>
         </is>
@@ -488,15 +493,18 @@
         <v>-5.5e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.6369</v>
+        <v>-16.64</v>
       </c>
       <c r="F2" t="n">
+        <v>-35.29</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.3898</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.555</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>0.9323</v>
       </c>
     </row>
@@ -518,15 +526,18 @@
         <v>-0.000124</v>
       </c>
       <c r="E3" t="n">
-        <v>-37.2771</v>
+        <v>-37.28</v>
       </c>
       <c r="F3" t="n">
+        <v>-59.8</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.1879</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.982</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>0.2444</v>
       </c>
     </row>
@@ -548,15 +559,18 @@
         <v>-4.1e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>-12.3499</v>
+        <v>-12.35</v>
       </c>
       <c r="F4" t="n">
+        <v>-40.69</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.5289</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1.223</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>0.9347</v>
       </c>
     </row>
@@ -578,15 +592,18 @@
         <v>-4.8e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>-14.3455</v>
+        <v>-14.35</v>
       </c>
       <c r="F5" t="n">
+        <v>-43.7</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.5451</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1.117</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>0.8788</v>
       </c>
     </row>
@@ -608,15 +625,18 @@
         <v>-4.8e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>-14.4749</v>
+        <v>-14.47</v>
       </c>
       <c r="F6" t="n">
+        <v>-44.04</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.3796</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1.317</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>0.8424</v>
       </c>
     </row>
@@ -638,15 +658,18 @@
         <v>-6.8e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>-20.4338</v>
+        <v>-20.43</v>
       </c>
       <c r="F7" t="n">
+        <v>-48.81</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.2681</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.281</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>0.4125</v>
       </c>
     </row>
@@ -668,15 +691,18 @@
         <v>-5.6e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.8025</v>
+        <v>-16.8</v>
       </c>
       <c r="F8" t="n">
+        <v>-44.29</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.4913</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.14</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.7803</v>
       </c>
     </row>
@@ -698,15 +724,18 @@
         <v>-6.499999999999999e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.3429</v>
+        <v>-19.34</v>
       </c>
       <c r="F9" t="n">
+        <v>-45.36</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.4258</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.119</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>0.5682</v>
       </c>
     </row>
@@ -728,15 +757,18 @@
         <v>-7.8e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>-23.4498</v>
+        <v>-23.45</v>
       </c>
       <c r="F10" t="n">
+        <v>-46.56</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.4244</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.264</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>0.7702</v>
       </c>
     </row>
@@ -758,15 +790,18 @@
         <v>-9.1e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-27.4297</v>
+        <v>-27.43</v>
       </c>
       <c r="F11" t="n">
+        <v>-48.48</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.3821</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.244</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>0.6911</v>
       </c>
     </row>
@@ -788,15 +823,18 @@
         <v>-9.2e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>-27.5046</v>
+        <v>-27.5</v>
       </c>
       <c r="F12" t="n">
+        <v>-48.22</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.3988</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>1.093</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>0.5226</v>
       </c>
     </row>
@@ -818,15 +856,18 @@
         <v>-0.000107</v>
       </c>
       <c r="E13" t="n">
-        <v>-32.0071</v>
+        <v>-32.01</v>
       </c>
       <c r="F13" t="n">
+        <v>-50.44</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.3881</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>1.063</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.4802</v>
       </c>
     </row>
@@ -848,15 +889,18 @@
         <v>-0.000121</v>
       </c>
       <c r="E14" t="n">
-        <v>-36.2429</v>
+        <v>-36.24</v>
       </c>
       <c r="F14" t="n">
+        <v>-59.37</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.269</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1.081</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>0.4337</v>
       </c>
     </row>
@@ -878,15 +922,18 @@
         <v>-0.00014</v>
       </c>
       <c r="E15" t="n">
-        <v>-42.063</v>
+        <v>-42.06</v>
       </c>
       <c r="F15" t="n">
+        <v>-65.98999999999999</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.2086</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.959</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>0.2413</v>
       </c>
     </row>
@@ -908,15 +955,18 @@
         <v>-0.000101</v>
       </c>
       <c r="E16" t="n">
-        <v>-30.3483</v>
+        <v>-30.35</v>
       </c>
       <c r="F16" t="n">
+        <v>-56.85</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.3547</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1.051</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.4543</v>
       </c>
     </row>
@@ -938,15 +988,18 @@
         <v>-9.7e-05</v>
       </c>
       <c r="E17" t="n">
-        <v>-29.0068</v>
+        <v>-29.01</v>
       </c>
       <c r="F17" t="n">
+        <v>-56.66</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.3875</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>1.134</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.6049</v>
       </c>
     </row>
@@ -968,15 +1021,18 @@
         <v>-9.8e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>-29.5136</v>
+        <v>-29.51</v>
       </c>
       <c r="F18" t="n">
+        <v>-57.33</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.3471</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1.111</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>0.5417</v>
       </c>
     </row>
@@ -998,15 +1054,18 @@
         <v>-0.000102</v>
       </c>
       <c r="E19" t="n">
-        <v>-30.6728</v>
+        <v>-30.67</v>
       </c>
       <c r="F19" t="n">
+        <v>-60.16</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.3028</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1.096</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>0.469</v>
       </c>
     </row>
@@ -1028,16 +1087,118 @@
         <v>-0.000108</v>
       </c>
       <c r="E20" t="n">
-        <v>-32.2395</v>
+        <v>-32.24</v>
       </c>
       <c r="F20" t="n">
+        <v>-61.75</v>
+      </c>
+      <c r="G20" t="n">
         <v>0.2979</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>1.046</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>0.4257</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Septiembre 14-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6562.115</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.000106</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-31.84</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-60.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.182</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6012</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6562.034</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.000119</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-35.54</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-63.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7144</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8494</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Septiembre 29-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6562.069</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.000113</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-33.92</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5419</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7276</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
@@ -487,25 +487,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6562.448</v>
+        <v>6562.187</v>
       </c>
       <c r="D2" t="n">
-        <v>-5.5e-05</v>
+        <v>-9.500000000000001e-05</v>
       </c>
       <c r="E2" t="n">
-        <v>-16.64</v>
+        <v>-28.55</v>
       </c>
       <c r="F2" t="n">
-        <v>-35.29</v>
+        <v>-47.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3898</v>
+        <v>0.2849</v>
       </c>
       <c r="H2" t="n">
-        <v>1.555</v>
+        <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9323</v>
+        <v>0.5462</v>
       </c>
     </row>
     <row r="3">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6561.996</v>
+        <v>6561.995</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000124</v>
+        <v>-0.000125</v>
       </c>
       <c r="E3" t="n">
-        <v>-37.28</v>
+        <v>-37.33</v>
       </c>
       <c r="F3" t="n">
-        <v>-59.8</v>
+        <v>-59.85</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1879</v>
+        <v>0.1877</v>
       </c>
       <c r="H3" t="n">
-        <v>0.982</v>
+        <v>0.981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2444</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="4">
@@ -553,25 +553,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6562.542</v>
+        <v>6562.391</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.1e-05</v>
+        <v>-6.4e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>-12.35</v>
+        <v>-19.22</v>
       </c>
       <c r="F4" t="n">
-        <v>-40.69</v>
+        <v>-47.56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5289</v>
+        <v>0.3317</v>
       </c>
       <c r="H4" t="n">
-        <v>1.223</v>
+        <v>1.214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9347</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="5">
@@ -586,25 +586,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6562.498</v>
+        <v>6562.446</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.8e-05</v>
+        <v>-5.6e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>-14.35</v>
+        <v>-16.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-43.7</v>
+        <v>-46.05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5451</v>
+        <v>0.4656</v>
       </c>
       <c r="H5" t="n">
-        <v>1.117</v>
+        <v>1.108</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8788</v>
+        <v>0.7116</v>
       </c>
     </row>
     <row r="6">
@@ -619,25 +619,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6562.495</v>
+        <v>6562.32</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.8e-05</v>
+        <v>-7.499999999999999e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>-14.47</v>
+        <v>-22.47</v>
       </c>
       <c r="F6" t="n">
-        <v>-44.04</v>
+        <v>-52.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3796</v>
+        <v>0.2589</v>
       </c>
       <c r="H6" t="n">
-        <v>1.317</v>
+        <v>1.341</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8424</v>
+        <v>0.4988</v>
       </c>
     </row>
     <row r="7">
@@ -652,25 +652,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6562.365</v>
+        <v>6562.254</v>
       </c>
       <c r="D7" t="n">
-        <v>-6.8e-05</v>
+        <v>-8.500000000000001e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>-20.43</v>
+        <v>-25.49</v>
       </c>
       <c r="F7" t="n">
-        <v>-48.81</v>
+        <v>-53.87</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2681</v>
+        <v>0.2312</v>
       </c>
       <c r="H7" t="n">
-        <v>1.281</v>
+        <v>1.177</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4125</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="8">
@@ -685,25 +685,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6562.444</v>
+        <v>6562.396</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6e-05</v>
+        <v>-6.3e-05</v>
       </c>
       <c r="E8" t="n">
-        <v>-16.8</v>
+        <v>-18.99</v>
       </c>
       <c r="F8" t="n">
-        <v>-44.29</v>
+        <v>-46.48</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4913</v>
+        <v>0.4129</v>
       </c>
       <c r="H8" t="n">
-        <v>1.14</v>
+        <v>1.111</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7803</v>
+        <v>0.6548</v>
       </c>
     </row>
     <row r="9">
@@ -718,25 +718,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6562.389</v>
+        <v>6562.36</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.499999999999999e-05</v>
+        <v>-6.9e-05</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.34</v>
+        <v>-20.65</v>
       </c>
       <c r="F9" t="n">
-        <v>-45.36</v>
+        <v>-46.67</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4258</v>
+        <v>0.3915</v>
       </c>
       <c r="H9" t="n">
-        <v>1.119</v>
+        <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5682</v>
+        <v>0.5137</v>
       </c>
     </row>
     <row r="10">
@@ -751,25 +751,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6562.299</v>
+        <v>6562.282</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.8e-05</v>
+        <v>-8.1e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>-23.45</v>
+        <v>-24.22</v>
       </c>
       <c r="F10" t="n">
-        <v>-46.56</v>
+        <v>-47.33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4244</v>
+        <v>0.387</v>
       </c>
       <c r="H10" t="n">
-        <v>1.264</v>
+        <v>1.261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7702</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="11">
@@ -784,25 +784,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6562.212</v>
+        <v>6562.24</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.1e-05</v>
+        <v>-8.7e-05</v>
       </c>
       <c r="E11" t="n">
-        <v>-27.43</v>
+        <v>-26.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-48.48</v>
+        <v>-47.17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3821</v>
+        <v>0.392</v>
       </c>
       <c r="H11" t="n">
-        <v>1.244</v>
+        <v>1.248</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6911</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="12">
@@ -817,25 +817,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6562.21</v>
+        <v>6562.184</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.2e-05</v>
+        <v>-9.6e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>-27.5</v>
+        <v>-28.69</v>
       </c>
       <c r="F12" t="n">
-        <v>-48.22</v>
+        <v>-49.41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3988</v>
+        <v>0.345</v>
       </c>
       <c r="H12" t="n">
-        <v>1.093</v>
+        <v>1.101</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5226</v>
+        <v>0.4551</v>
       </c>
     </row>
     <row r="13">
@@ -856,19 +856,19 @@
         <v>-0.000107</v>
       </c>
       <c r="E13" t="n">
-        <v>-32.01</v>
+        <v>-32</v>
       </c>
       <c r="F13" t="n">
-        <v>-50.44</v>
+        <v>-50.43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3881</v>
+        <v>0.5853</v>
       </c>
       <c r="H13" t="n">
-        <v>1.063</v>
+        <v>1.013</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4802</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="14">
@@ -883,25 +883,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6562.019</v>
+        <v>6561.993</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.000121</v>
+        <v>-0.000125</v>
       </c>
       <c r="E14" t="n">
-        <v>-36.24</v>
+        <v>-37.43</v>
       </c>
       <c r="F14" t="n">
-        <v>-59.37</v>
+        <v>-60.56</v>
       </c>
       <c r="G14" t="n">
-        <v>0.269</v>
+        <v>0.2545</v>
       </c>
       <c r="H14" t="n">
-        <v>1.081</v>
+        <v>1.065</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4337</v>
+        <v>0.4065</v>
       </c>
     </row>
     <row r="15">
@@ -916,25 +916,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6561.891</v>
+        <v>6561.89</v>
       </c>
       <c r="D15" t="n">
         <v>-0.00014</v>
       </c>
       <c r="E15" t="n">
-        <v>-42.06</v>
+        <v>-42.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-65.98999999999999</v>
+        <v>-66.03</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2086</v>
+        <v>0.2088</v>
       </c>
       <c r="H15" t="n">
-        <v>0.959</v>
+        <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2413</v>
+        <v>0.2419</v>
       </c>
     </row>
     <row r="16">
@@ -949,25 +949,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6562.148</v>
+        <v>6561.993</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.000101</v>
+        <v>-0.000125</v>
       </c>
       <c r="E16" t="n">
-        <v>-30.35</v>
+        <v>-37.42</v>
       </c>
       <c r="F16" t="n">
-        <v>-56.85</v>
+        <v>-63.92</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3547</v>
+        <v>0.2188</v>
       </c>
       <c r="H16" t="n">
-        <v>1.051</v>
+        <v>0.924</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4543</v>
+        <v>0.2463</v>
       </c>
     </row>
     <row r="17">
@@ -982,25 +982,25 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6562.177</v>
+        <v>6562.1</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.7e-05</v>
+        <v>-0.000109</v>
       </c>
       <c r="E17" t="n">
-        <v>-29.01</v>
+        <v>-32.54</v>
       </c>
       <c r="F17" t="n">
-        <v>-56.66</v>
+        <v>-60.19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3875</v>
+        <v>0.3017</v>
       </c>
       <c r="H17" t="n">
-        <v>1.134</v>
+        <v>1.091</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6049</v>
+        <v>0.4608</v>
       </c>
     </row>
     <row r="18">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6562.166</v>
+        <v>6562.031</v>
       </c>
       <c r="D18" t="n">
-        <v>-9.8e-05</v>
+        <v>-0.000119</v>
       </c>
       <c r="E18" t="n">
-        <v>-29.51</v>
+        <v>-35.67</v>
       </c>
       <c r="F18" t="n">
-        <v>-57.33</v>
+        <v>-63.49</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3471</v>
+        <v>0.2329</v>
       </c>
       <c r="H18" t="n">
-        <v>1.111</v>
+        <v>1.038</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5417</v>
+        <v>0.3587</v>
       </c>
     </row>
     <row r="19">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6562.141</v>
+        <v>6562.099</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.000102</v>
+        <v>-0.000109</v>
       </c>
       <c r="E19" t="n">
-        <v>-30.67</v>
+        <v>-32.59</v>
       </c>
       <c r="F19" t="n">
-        <v>-60.16</v>
+        <v>-62.08</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3028</v>
+        <v>0.2755</v>
       </c>
       <c r="H19" t="n">
-        <v>1.096</v>
+        <v>1.067</v>
       </c>
       <c r="I19" t="n">
-        <v>0.469</v>
+        <v>0.3939</v>
       </c>
     </row>
     <row r="20">
@@ -1081,25 +1081,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.106</v>
+        <v>6562.114</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.000108</v>
+        <v>-0.000106</v>
       </c>
       <c r="E20" t="n">
-        <v>-32.24</v>
+        <v>-31.87</v>
       </c>
       <c r="F20" t="n">
-        <v>-61.75</v>
+        <v>-61.38</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2979</v>
+        <v>0.3095</v>
       </c>
       <c r="H20" t="n">
-        <v>1.046</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4257</v>
+        <v>0.4263</v>
       </c>
     </row>
     <row r="21">
@@ -1114,25 +1114,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6562.115</v>
+        <v>6562.058</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.000106</v>
+        <v>-0.000115</v>
       </c>
       <c r="E21" t="n">
-        <v>-31.84</v>
+        <v>-34.42</v>
       </c>
       <c r="F21" t="n">
-        <v>-60.8</v>
+        <v>-63.38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3328</v>
+        <v>0.2949</v>
       </c>
       <c r="H21" t="n">
-        <v>1.182</v>
+        <v>1.058</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6012</v>
+        <v>0.4165</v>
       </c>
     </row>
     <row r="22">
@@ -1159,13 +1159,13 @@
         <v>-63.75</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7144</v>
+        <v>0.7145</v>
       </c>
       <c r="H22" t="n">
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8494</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="23">
@@ -1180,25 +1180,25 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6562.069</v>
+        <v>6562.032</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.000113</v>
+        <v>-0.000119</v>
       </c>
       <c r="E23" t="n">
-        <v>-33.92</v>
+        <v>-35.64</v>
       </c>
       <c r="F23" t="n">
-        <v>-60.5</v>
+        <v>-62.22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5419</v>
+        <v>0.5748</v>
       </c>
       <c r="H23" t="n">
-        <v>1.044</v>
+        <v>1.027</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7276</v>
+        <v>0.7226</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
@@ -489,8 +489,10 @@
       <c r="C2" t="n">
         <v>6562.187</v>
       </c>
-      <c r="D2" t="n">
-        <v>-9.500000000000001e-05</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-9.5e-05</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>-28.55</v>
@@ -499,13 +501,13 @@
         <v>-47.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2849</v>
+        <v>0.28</v>
       </c>
       <c r="H2" t="n">
         <v>1.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5462</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="3">
@@ -522,8 +524,10 @@
       <c r="C3" t="n">
         <v>6561.995</v>
       </c>
-      <c r="D3" t="n">
-        <v>-0.000125</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>-37.33</v>
@@ -532,13 +536,13 @@
         <v>-59.85</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1877</v>
+        <v>0.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="I3" t="n">
-        <v>0.243</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="4">
@@ -555,8 +559,10 @@
       <c r="C4" t="n">
         <v>6562.391</v>
       </c>
-      <c r="D4" t="n">
-        <v>-6.4e-05</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-6.4e-05</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>-19.22</v>
@@ -565,13 +571,13 @@
         <v>-47.56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3317</v>
+        <v>0.33</v>
       </c>
       <c r="H4" t="n">
-        <v>1.214</v>
+        <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5911</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="5">
@@ -588,8 +594,10 @@
       <c r="C5" t="n">
         <v>6562.446</v>
       </c>
-      <c r="D5" t="n">
-        <v>-5.6e-05</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-5.6e-05</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>-16.7</v>
@@ -598,13 +606,13 @@
         <v>-46.05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4656</v>
+        <v>0.47</v>
       </c>
       <c r="H5" t="n">
-        <v>1.108</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7116</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="6">
@@ -621,8 +629,10 @@
       <c r="C6" t="n">
         <v>6562.32</v>
       </c>
-      <c r="D6" t="n">
-        <v>-7.499999999999999e-05</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-7.5e-05</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>-22.47</v>
@@ -631,13 +641,13 @@
         <v>-52.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2589</v>
+        <v>0.26</v>
       </c>
       <c r="H6" t="n">
-        <v>1.341</v>
+        <v>1.34</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4988</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -654,8 +664,10 @@
       <c r="C7" t="n">
         <v>6562.254</v>
       </c>
-      <c r="D7" t="n">
-        <v>-8.500000000000001e-05</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-8.5e-05</t>
+        </is>
       </c>
       <c r="E7" t="n">
         <v>-25.49</v>
@@ -664,13 +676,13 @@
         <v>-53.87</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2312</v>
+        <v>0.23</v>
       </c>
       <c r="H7" t="n">
-        <v>1.177</v>
+        <v>1.18</v>
       </c>
       <c r="I7" t="n">
-        <v>0.327</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
@@ -687,8 +699,10 @@
       <c r="C8" t="n">
         <v>6562.396</v>
       </c>
-      <c r="D8" t="n">
-        <v>-6.3e-05</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-6.3e-05</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>-18.99</v>
@@ -697,13 +711,13 @@
         <v>-46.48</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4129</v>
+        <v>0.41</v>
       </c>
       <c r="H8" t="n">
-        <v>1.111</v>
+        <v>1.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6548</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="9">
@@ -720,8 +734,10 @@
       <c r="C9" t="n">
         <v>6562.36</v>
       </c>
-      <c r="D9" t="n">
-        <v>-6.9e-05</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-6.9e-05</t>
+        </is>
       </c>
       <c r="E9" t="n">
         <v>-20.65</v>
@@ -730,13 +746,13 @@
         <v>-46.67</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3915</v>
+        <v>0.39</v>
       </c>
       <c r="H9" t="n">
         <v>1.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5137</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="10">
@@ -753,8 +769,10 @@
       <c r="C10" t="n">
         <v>6562.282</v>
       </c>
-      <c r="D10" t="n">
-        <v>-8.1e-05</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-8.1e-05</t>
+        </is>
       </c>
       <c r="E10" t="n">
         <v>-24.22</v>
@@ -763,13 +781,13 @@
         <v>-47.33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.387</v>
+        <v>0.39</v>
       </c>
       <c r="H10" t="n">
-        <v>1.261</v>
+        <v>1.26</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6253</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="11">
@@ -786,8 +804,10 @@
       <c r="C11" t="n">
         <v>6562.24</v>
       </c>
-      <c r="D11" t="n">
-        <v>-8.7e-05</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-8.7e-05</t>
+        </is>
       </c>
       <c r="E11" t="n">
         <v>-26.12</v>
@@ -796,13 +816,13 @@
         <v>-47.17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.392</v>
+        <v>0.39</v>
       </c>
       <c r="H11" t="n">
-        <v>1.248</v>
+        <v>1.25</v>
       </c>
       <c r="I11" t="n">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="12">
@@ -819,8 +839,10 @@
       <c r="C12" t="n">
         <v>6562.184</v>
       </c>
-      <c r="D12" t="n">
-        <v>-9.6e-05</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-9.6e-05</t>
+        </is>
       </c>
       <c r="E12" t="n">
         <v>-28.69</v>
@@ -829,13 +851,13 @@
         <v>-49.41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="H12" t="n">
-        <v>1.101</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4551</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="13">
@@ -852,8 +874,10 @@
       <c r="C13" t="n">
         <v>6562.111</v>
       </c>
-      <c r="D13" t="n">
-        <v>-0.000107</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>-32</v>
@@ -862,13 +886,13 @@
         <v>-50.43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5853</v>
+        <v>0.59</v>
       </c>
       <c r="H13" t="n">
-        <v>1.013</v>
+        <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6923</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -885,8 +909,10 @@
       <c r="C14" t="n">
         <v>6561.993</v>
       </c>
-      <c r="D14" t="n">
-        <v>-0.000125</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E14" t="n">
         <v>-37.43</v>
@@ -895,13 +921,13 @@
         <v>-60.56</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2545</v>
+        <v>0.25</v>
       </c>
       <c r="H14" t="n">
-        <v>1.065</v>
+        <v>1.07</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4065</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15">
@@ -918,8 +944,10 @@
       <c r="C15" t="n">
         <v>6561.89</v>
       </c>
-      <c r="D15" t="n">
-        <v>-0.00014</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-0.00014</t>
+        </is>
       </c>
       <c r="E15" t="n">
         <v>-42.1</v>
@@ -928,13 +956,13 @@
         <v>-66.03</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2088</v>
+        <v>0.21</v>
       </c>
       <c r="H15" t="n">
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2419</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="16">
@@ -951,8 +979,10 @@
       <c r="C16" t="n">
         <v>6561.993</v>
       </c>
-      <c r="D16" t="n">
-        <v>-0.000125</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E16" t="n">
         <v>-37.42</v>
@@ -961,13 +991,13 @@
         <v>-63.92</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2188</v>
+        <v>0.22</v>
       </c>
       <c r="H16" t="n">
-        <v>0.924</v>
+        <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2463</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="17">
@@ -984,8 +1014,10 @@
       <c r="C17" t="n">
         <v>6562.1</v>
       </c>
-      <c r="D17" t="n">
-        <v>-0.000109</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E17" t="n">
         <v>-32.54</v>
@@ -994,13 +1026,13 @@
         <v>-60.19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3017</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.091</v>
+        <v>1.09</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4608</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="18">
@@ -1017,8 +1049,10 @@
       <c r="C18" t="n">
         <v>6562.031</v>
       </c>
-      <c r="D18" t="n">
-        <v>-0.000119</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E18" t="n">
         <v>-35.67</v>
@@ -1027,13 +1061,13 @@
         <v>-63.49</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2329</v>
+        <v>0.23</v>
       </c>
       <c r="H18" t="n">
-        <v>1.038</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3587</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="19">
@@ -1050,8 +1084,10 @@
       <c r="C19" t="n">
         <v>6562.099</v>
       </c>
-      <c r="D19" t="n">
-        <v>-0.000109</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E19" t="n">
         <v>-32.59</v>
@@ -1060,13 +1096,13 @@
         <v>-62.08</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2755</v>
+        <v>0.28</v>
       </c>
       <c r="H19" t="n">
-        <v>1.067</v>
+        <v>1.07</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3939</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="20">
@@ -1083,8 +1119,10 @@
       <c r="C20" t="n">
         <v>6562.114</v>
       </c>
-      <c r="D20" t="n">
-        <v>-0.000106</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E20" t="n">
         <v>-31.87</v>
@@ -1093,13 +1131,13 @@
         <v>-61.38</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3095</v>
+        <v>0.31</v>
       </c>
       <c r="H20" t="n">
         <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4263</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="21">
@@ -1116,8 +1154,10 @@
       <c r="C21" t="n">
         <v>6562.058</v>
       </c>
-      <c r="D21" t="n">
-        <v>-0.000115</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-0.00011</t>
+        </is>
       </c>
       <c r="E21" t="n">
         <v>-34.42</v>
@@ -1126,13 +1166,13 @@
         <v>-63.38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2949</v>
+        <v>0.29</v>
       </c>
       <c r="H21" t="n">
-        <v>1.058</v>
+        <v>1.06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4165</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="22">
@@ -1149,8 +1189,10 @@
       <c r="C22" t="n">
         <v>6562.034</v>
       </c>
-      <c r="D22" t="n">
-        <v>-0.000119</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E22" t="n">
         <v>-35.54</v>
@@ -1159,13 +1201,13 @@
         <v>-63.75</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7145</v>
+        <v>0.71</v>
       </c>
       <c r="H22" t="n">
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8495</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23">
@@ -1182,8 +1224,10 @@
       <c r="C23" t="n">
         <v>6562.032</v>
       </c>
-      <c r="D23" t="n">
-        <v>-0.000119</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
       </c>
       <c r="E23" t="n">
         <v>-35.64</v>
@@ -1192,13 +1236,13 @@
         <v>-62.22</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5748</v>
+        <v>0.57</v>
       </c>
       <c r="H23" t="n">
-        <v>1.027</v>
+        <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7226</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/Resultados emisión azul halpha 2024, 2025 y 2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,7 +898,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Julio 24-2026</t>
+          <t>Agosto 19-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -907,33 +907,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6561.993</v>
+        <v>6562.084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-37.43</v>
+        <v>-33.26</v>
       </c>
       <c r="F14" t="n">
-        <v>-60.56</v>
+        <v>-62.06</v>
       </c>
       <c r="G14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julio 27-2026</t>
+          <t>Julio 24-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -942,33 +942,33 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6561.89</v>
+        <v>6561.993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-0.00014</t>
+          <t>-0.00012</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-42.1</v>
+        <v>-37.43</v>
       </c>
       <c r="F15" t="n">
-        <v>-66.03</v>
+        <v>-60.56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.96</v>
+        <v>1.07</v>
       </c>
       <c r="I15" t="n">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agosto 06-2026</t>
+          <t>Julio 27-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -977,33 +977,33 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6561.993</v>
+        <v>6561.89</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00014</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-37.42</v>
+        <v>-42.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-63.92</v>
+        <v>-66.03</v>
       </c>
       <c r="G16" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H16" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="I16" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agosto 10-2026</t>
+          <t>Agosto 06-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1012,33 +1012,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6562.1</v>
+        <v>6561.993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-0.00011</t>
+          <t>-0.00012</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-32.54</v>
+        <v>-37.42</v>
       </c>
       <c r="F17" t="n">
-        <v>-60.19</v>
+        <v>-63.92</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>0.92</v>
       </c>
       <c r="I17" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Agosto 13-2026</t>
+          <t>Agosto 10-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1047,33 +1047,33 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6562.031</v>
+        <v>6562.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>-35.67</v>
+        <v>-32.54</v>
       </c>
       <c r="F18" t="n">
-        <v>-63.49</v>
+        <v>-60.19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agosto 28-2026</t>
+          <t>Agosto 13-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1082,33 +1082,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6562.099</v>
+        <v>6562.031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-0.00011</t>
+          <t>-0.00012</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-32.59</v>
+        <v>-35.67</v>
       </c>
       <c r="F19" t="n">
-        <v>-62.08</v>
+        <v>-63.49</v>
       </c>
       <c r="G19" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H19" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Septiembre 07-2026</t>
+          <t>Agosto 28-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6562.114</v>
+        <v>6562.099</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1125,25 +1125,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-31.87</v>
+        <v>-32.59</v>
       </c>
       <c r="F20" t="n">
-        <v>-61.38</v>
+        <v>-62.08</v>
       </c>
       <c r="G20" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="I20" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Septiembre 14-2026</t>
+          <t>Septiembre 07-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6562.058</v>
+        <v>6562.114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1160,25 +1160,25 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>-34.42</v>
+        <v>-31.87</v>
       </c>
       <c r="F21" t="n">
-        <v>-63.38</v>
+        <v>-61.38</v>
       </c>
       <c r="G21" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Septiembre 21-2026</t>
+          <t>Septiembre 14-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1187,62 +1187,132 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6562.034</v>
+        <v>6562.058</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.00012</t>
+          <t>-0.00011</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-35.54</v>
+        <v>-34.42</v>
       </c>
       <c r="F22" t="n">
-        <v>-63.75</v>
+        <v>-63.38</v>
       </c>
       <c r="G22" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.85</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Septiembre 21-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6562.034</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-0.00012</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>-35.54</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-63.75</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Septiembre 29-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Emisión Azul Hα</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>6562.032</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>-0.00012</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-35.64</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-62.22</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>0.57</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>1.03</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Octubre 16-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Emisión Azul Hα</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6561.934</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-0.00013</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>-40.1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-61.71</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>
